--- a/output/pdf_financials_xlsx/DMED.xlsx
+++ b/output/pdf_financials_xlsx/DMED.xlsx
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.277935</v>
+        <v>-1.277935</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.501057</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.277935</v>
+        <v>-1.277935</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.501057</v>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.277935</v>
+        <v>-1.277935</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.501057</v>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.277935</v>
+        <v>-1.277935</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.501057</v>
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.277935</v>
+        <v>-1.277935</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.501057</v>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1.277935</v>
+        <v>-1.277935</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>0.501057</v>
+        <v>-0.501057</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/DMED.xlsx
+++ b/output/pdf_financials_xlsx/DMED.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00589</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.008666</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.002607</v>
       </c>
     </row>
     <row r="13">
@@ -869,13 +869,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.277935</v>
+        <v>-1.272045</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.501057</v>
+        <v>-0.509723</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.403145</v>
+        <v>-1.405752</v>
       </c>
     </row>
     <row r="28">
@@ -901,13 +901,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.277935</v>
+        <v>-1.272045</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.501057</v>
+        <v>-0.509723</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.403145</v>
+        <v>-1.405752</v>
       </c>
     </row>
     <row r="30">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
